--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484759_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484759_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.276899999999999</v>
+        <v>8.494400000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0913</v>
+        <v>6.1501</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1856</v>
+        <v>2.3443</v>
       </c>
       <c r="G2" t="n">
         <v>6.5012</v>
@@ -610,13 +610,13 @@
         <v>1.1322</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0241</v>
+        <v>0.1934</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0029</v>
+        <v>0.0617</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.027</v>
+        <v>0.1317</v>
       </c>
       <c r="V2" t="n">
         <v>2.5546</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1733</v>
+        <v>6.8709</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5477</v>
+        <v>6.4834</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6257</v>
+        <v>0.3876</v>
       </c>
       <c r="G3" t="n">
         <v>6.154</v>
@@ -688,13 +688,13 @@
         <v>1.5096</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2451</v>
+        <v>0.4525</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7055</v>
+        <v>0.2302</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4604</v>
+        <v>0.2223</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2452</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.1353</v>
+        <v>6.3246</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7116</v>
+        <v>3.9009</v>
       </c>
       <c r="F4" t="n">
         <v>2.4237</v>
@@ -766,10 +766,10 @@
         <v>2.2644</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.368</v>
+        <v>0.8214</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7519</v>
+        <v>0.4374</v>
       </c>
       <c r="U4" t="n">
         <v>0.3839</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.1327</v>
+        <v>2.9634</v>
       </c>
       <c r="E5" t="n">
-        <v>5.6894</v>
+        <v>3.1763</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5567</v>
+        <v>-0.2128</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7177</v>
@@ -844,13 +844,13 @@
         <v>2.0757</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4088</v>
+        <v>1.2396</v>
       </c>
       <c r="T5" t="n">
-        <v>4.0302</v>
+        <v>1.517</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6213</v>
+        <v>-0.2774</v>
       </c>
       <c r="V5" t="n">
         <v>1.3094</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. ANZULUNI</t>
+          <t>J. NÚÑEZ NIEVAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8789</v>
+        <v>0.6339</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1554</v>
+        <v>0.6339</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0343</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6523</v>
+        <v>0.6339</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6096</v>
+        <v>0.6339</v>
       </c>
       <c r="I6" t="n">
-        <v>1.262</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7109</v>
+        <v>0.6339</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5534</v>
+        <v>0.6339</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1575</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0586</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.1631</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.1045</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.4531</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.7175</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2644</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3703</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.606</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7643</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3094</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.06419999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. NÚÑEZ NIEVAS</t>
+          <t>M. MARTIN MARTINEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6339</v>
+        <v>0.5206</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6339</v>
+        <v>0.6564</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-0.1358</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6339</v>
+        <v>1.721</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6339</v>
+        <v>1.3594</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.3617</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6339</v>
+        <v>0.9318</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6339</v>
+        <v>1.458</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.5262</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.7892</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.8878</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.5661</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.5661</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0.2195</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.0559</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. DIAZ MUNOZ</t>
+          <t>B. ZHENG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4532</v>
+        <v>0.2615</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4144</v>
+        <v>0.8484</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0388</v>
+        <v>-0.587</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5256</v>
+        <v>-2.7296</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.504</v>
+        <v>-2.9613</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0216</v>
+        <v>0.2317</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0.4646</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.5228</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.0582</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5256</v>
+        <v>-2.265</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.504</v>
+        <v>-2.4386</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0216</v>
+        <v>0.1736</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1887</v>
+        <v>1.6983</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1887</v>
+        <v>1.6983</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7901</v>
+        <v>-0.0356</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4144</v>
+        <v>0.0679</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3757</v>
+        <v>-0.1034</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.3283</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.08309999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. MARTIN MARTINEZ</t>
+          <t>P. DIAZ MUNOZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1141</v>
+        <v>0.0467</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4615</v>
+        <v>0.2195</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3474</v>
+        <v>-0.1728</v>
       </c>
       <c r="G9" t="n">
-        <v>1.721</v>
+        <v>-0.5256</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3594</v>
+        <v>-0.504</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3617</v>
+        <v>-0.0216</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9318</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1.458</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5262</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7892</v>
+        <v>-0.5256</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.504</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8878</v>
+        <v>-0.0216</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5661</v>
+        <v>0.1887</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5661</v>
+        <v>0.1887</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.626</v>
+        <v>0.3836</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4703</v>
+        <v>0.2195</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1557</v>
+        <v>0.164</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. ZHENG</t>
+          <t>M. ANZULUNI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5406</v>
+        <v>0.037</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2051</v>
+        <v>-1.3889</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7457</v>
+        <v>1.4259</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.7296</v>
+        <v>0.6523</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.9613</v>
+        <v>-0.6096</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2317</v>
+        <v>1.262</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4646</v>
+        <v>1.7109</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5228</v>
+        <v>1.5534</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0582</v>
+        <v>0.1575</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.265</v>
+        <v>-1.0586</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.4386</v>
+        <v>-2.1631</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1736</v>
+        <v>1.1045</v>
       </c>
       <c r="P10" t="n">
-        <v>1.6983</v>
+        <v>-2.4531</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-4.7175</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6983</v>
+        <v>2.2644</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8377</v>
+        <v>0.5284</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5755</v>
+        <v>0.3725</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2621</v>
+        <v>0.1559</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3283</v>
+        <v>1.3094</v>
       </c>
       <c r="W10" t="n">
         <v>1.2452</v>
       </c>
       <c r="X10" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.06419999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9978</v>
+        <v>-0.3196</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3999</v>
+        <v>0.146</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5979</v>
+        <v>-0.4656</v>
       </c>
       <c r="G11" t="n">
         <v>0.3423</v>
@@ -1312,13 +1312,13 @@
         <v>0.5661</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6419</v>
+        <v>0.0363</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5291</v>
+        <v>0.0169</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1129</v>
+        <v>0.0194</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3208</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2477</v>
+        <v>-2.682</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1055</v>
+        <v>-3.5927</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8578</v>
+        <v>0.9107</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7601</v>
@@ -1390,13 +1390,13 @@
         <v>0.5661</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8147</v>
+        <v>0.3805</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6525</v>
+        <v>0.1653</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1623</v>
+        <v>0.2152</v>
       </c>
       <c r="V12" t="n">
         <v>-0.038</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.3955</v>
+        <v>-3.947</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.2212</v>
+        <v>-2.7727</v>
       </c>
       <c r="F13" t="n">
         <v>-1.1743</v>
@@ -1468,10 +1468,10 @@
         <v>1.3209</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2845</v>
+        <v>0.164</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6343</v>
+        <v>-0.1858</v>
       </c>
       <c r="U13" t="n">
         <v>0.3498</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>18.61669999999999</v>
+        <v>19.2044</v>
       </c>
       <c r="E14" t="n">
-        <v>13.8729</v>
+        <v>14.4606</v>
       </c>
       <c r="F14" t="n">
-        <v>4.7439</v>
+        <v>4.743900000000001</v>
       </c>
       <c r="G14" t="n">
         <v>14.0718</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.6493999999999995</v>
+        <v>-0.6493999999999991</v>
       </c>
       <c r="I14" t="n">
         <v>14.7216</v>
@@ -1534,7 +1534,7 @@
         <v>-11.7936</v>
       </c>
       <c r="O14" t="n">
-        <v>7.255500000000001</v>
+        <v>7.2555</v>
       </c>
       <c r="P14" t="n">
         <v>-2.8305</v>
@@ -1546,13 +1546,13 @@
         <v>14.1525</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3566</v>
+        <v>3.9446</v>
       </c>
       <c r="T14" t="n">
-        <v>2.0394</v>
+        <v>2.6272</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3174</v>
+        <v>1.3173</v>
       </c>
       <c r="V14" t="n">
         <v>4.0185</v>
@@ -1561,13 +1561,13 @@
         <v>10.2064</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.1879</v>
+        <v>-6.187900000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. BLEDA MIRANDA</t>
+          <t>G. ESQUEMBRE MORUGAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4911</v>
+        <v>1.1543</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4148</v>
+        <v>0.6425</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0763</v>
+        <v>0.5118</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7087</v>
+        <v>1.371</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5329</v>
+        <v>0.3232</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1757</v>
+        <v>1.0478</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4606</v>
+        <v>0.7215</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7614</v>
+        <v>0.0634</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6992</v>
+        <v>0.6581</v>
       </c>
       <c r="M15" t="n">
-        <v>0.248</v>
+        <v>0.6496</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2285</v>
+        <v>0.2598</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4765</v>
+        <v>0.3897</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.5661</v>
+        <v>0.3774</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3209</v>
+        <v>0.3774</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9712</v>
+        <v>-0.2923</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8411999999999999</v>
+        <v>-0.0789</v>
       </c>
       <c r="U15" t="n">
-        <v>0.13</v>
+        <v>-0.2134</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6226</v>
+        <v>-0.3018</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6226</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. ESQUEMBRE MORUGAN</t>
+          <t>A. JAQUET</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9510999999999999</v>
+        <v>0.9863</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5451</v>
+        <v>0.5502</v>
       </c>
       <c r="F16" t="n">
-        <v>0.406</v>
+        <v>0.4362</v>
       </c>
       <c r="G16" t="n">
-        <v>1.371</v>
+        <v>1.0575</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3232</v>
+        <v>0.3021</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0478</v>
+        <v>0.7554</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7215</v>
+        <v>0.6677</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0634</v>
+        <v>0.0423</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6581</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6496</v>
+        <v>0.3897</v>
       </c>
       <c r="N16" t="n">
         <v>0.2598</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3897</v>
+        <v>0.1299</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3774</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3774</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4956</v>
+        <v>-0.0711</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1764</v>
+        <v>-0.1176</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3192</v>
+        <v>0.0465</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. JAQUET</t>
+          <t>C. BLEDA MIRANDA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8804999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5502</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3304</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0575</v>
+        <v>1.7087</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3021</v>
+        <v>0.5329</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7554</v>
+        <v>1.1757</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6677</v>
+        <v>1.4606</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0423</v>
+        <v>0.7614</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.6992</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3897</v>
+        <v>0.248</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2598</v>
+        <v>-0.2285</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1299</v>
+        <v>0.4765</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.3209</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1769</v>
+        <v>0.1401</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1176</v>
+        <v>0.354</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0594</v>
+        <v>-0.2139</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0116</v>
+        <v>0.3388</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1662</v>
+        <v>-0.9714</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1779</v>
+        <v>1.3101</v>
       </c>
       <c r="G18" t="n">
         <v>0.6982</v>
@@ -1858,13 +1858,13 @@
         <v>0.5661</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5244</v>
+        <v>-0.1972</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3527</v>
+        <v>-0.1579</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1716</v>
+        <v>-0.0394</v>
       </c>
       <c r="V18" t="n">
         <v>0.2152</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. TUDELA GARCIA</t>
+          <t>J. CONNELLY IV</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0985</v>
+        <v>-0.067</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5818</v>
+        <v>2.0777</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.6804</v>
+        <v>-2.1447</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.0895</v>
+        <v>-2.9002</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0611</v>
+        <v>-1.2459</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.0284</v>
+        <v>-1.6543</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1594</v>
+        <v>1.2116</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1097</v>
+        <v>1.2427</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0496</v>
+        <v>-0.0311</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.2488</v>
+        <v>-4.1117</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1708</v>
+        <v>-2.4886</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.0781</v>
+        <v>-1.6231</v>
       </c>
       <c r="P19" t="n">
         <v>0.5661</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5096</v>
+        <v>3.3966</v>
       </c>
       <c r="S19" t="n">
-        <v>2.7946</v>
+        <v>-0.4006</v>
       </c>
       <c r="T19" t="n">
-        <v>2.366</v>
+        <v>-0.3408</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4286</v>
+        <v>-0.0599</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.3697</v>
+        <v>2.6677</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>4.0374</v>
       </c>
       <c r="X19" t="n">
         <v>-1.3697</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. CONNELLY IV</t>
+          <t>K. FEDOROV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1995</v>
+        <v>-0.4292</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4931</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6926</v>
+        <v>-1.4126</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.9002</v>
+        <v>0.8531</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2459</v>
+        <v>0.641</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.6543</v>
+        <v>0.2122</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2116</v>
+        <v>3.0809</v>
       </c>
       <c r="K20" t="n">
-        <v>1.2427</v>
+        <v>3.0639</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0311</v>
+        <v>0.017</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.1117</v>
+        <v>-2.2278</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.4886</v>
+        <v>-2.4229</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.6231</v>
+        <v>0.1951</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5661</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.8305</v>
       </c>
       <c r="R20" t="n">
-        <v>3.3966</v>
+        <v>1.3209</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5331</v>
+        <v>-0.7161999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9254</v>
+        <v>-0.5122</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3922</v>
+        <v>-0.2039</v>
       </c>
       <c r="V20" t="n">
-        <v>2.6677</v>
+        <v>0.9434</v>
       </c>
       <c r="W20" t="n">
-        <v>4.0374</v>
+        <v>1.2452</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.3697</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. FEDOROV</t>
+          <t>G. TUDELA GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3486</v>
+        <v>-1.9521</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2757</v>
+        <v>0.7306</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6242</v>
+        <v>-2.6827</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8531</v>
+        <v>-2.0895</v>
       </c>
       <c r="H21" t="n">
-        <v>0.641</v>
+        <v>-0.0611</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2122</v>
+        <v>-2.0284</v>
       </c>
       <c r="J21" t="n">
-        <v>3.0809</v>
+        <v>1.1594</v>
       </c>
       <c r="K21" t="n">
-        <v>3.0639</v>
+        <v>1.1097</v>
       </c>
       <c r="L21" t="n">
-        <v>0.017</v>
+        <v>0.0496</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2278</v>
+        <v>-3.2488</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.4229</v>
+        <v>-1.1708</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1951</v>
+        <v>-2.0781</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5096</v>
+        <v>0.5661</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.8305</v>
+        <v>-0.9435</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3209</v>
+        <v>1.5096</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6355</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2199</v>
+        <v>0.5147</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4156</v>
+        <v>0.4262</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9434</v>
+        <v>-1.3697</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3018</v>
+        <v>-1.3697</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8227</v>
+        <v>-2.1347</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7529</v>
+        <v>-1.1683</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0698</v>
+        <v>-0.9664</v>
       </c>
       <c r="G22" t="n">
         <v>-2.8127</v>
@@ -2170,13 +2170,13 @@
         <v>2.8305</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1498</v>
+        <v>-0.4618</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5139</v>
+        <v>0.0708</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.636</v>
+        <v>-0.5325</v>
       </c>
       <c r="V22" t="n">
         <v>0.1963</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9371</v>
+        <v>-3.6726</v>
       </c>
       <c r="E23" t="n">
         <v>-2.3019</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6352</v>
+        <v>-1.3707</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0039</v>
@@ -2248,13 +2248,13 @@
         <v>0.5661</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6125</v>
+        <v>-0.348</v>
       </c>
       <c r="T23" t="n">
         <v>-0.5291</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0835</v>
+        <v>0.1811</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8868</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.7266</v>
+        <v>-4.8088</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08</v>
+        <v>0.762</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.8065</v>
+        <v>-5.5708</v>
       </c>
       <c r="G24" t="n">
         <v>-0.9315</v>
@@ -2326,13 +2326,13 @@
         <v>2.0757</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.569</v>
+        <v>-0.6512</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8818</v>
+        <v>-0.1998</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6872</v>
+        <v>-0.4514</v>
       </c>
       <c r="V24" t="n">
         <v>-3.4148</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.818</v>
+        <v>-8.042199999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.4635</v>
+        <v>-5.9764</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3545</v>
+        <v>-2.0658</v>
       </c>
       <c r="G25" t="n">
         <v>-9.0228</v>
@@ -2404,13 +2404,13 @@
         <v>3.0192</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.4256</v>
+        <v>-0.6497000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8078</v>
+        <v>-0.3206</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6178</v>
+        <v>-0.3291</v>
       </c>
       <c r="V25" t="n">
         <v>-0.4453</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-18.6167</v>
+        <v>-17.9672</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.7438</v>
+        <v>-4.744</v>
       </c>
       <c r="F26" t="n">
-        <v>-13.8726</v>
+        <v>-13.2232</v>
       </c>
       <c r="G26" t="n">
         <v>-14.0721</v>
@@ -2461,7 +2461,7 @@
         <v>11.7935</v>
       </c>
       <c r="L26" t="n">
-        <v>-7.2556</v>
+        <v>-7.255599999999999</v>
       </c>
       <c r="M26" t="n">
         <v>-18.61</v>
@@ -2482,13 +2482,13 @@
         <v>16.983</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.3566</v>
+        <v>-2.707</v>
       </c>
       <c r="T26" t="n">
         <v>-1.3174</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.0395</v>
+        <v>-1.3897</v>
       </c>
       <c r="V26" t="n">
         <v>-4.0184</v>
